--- a/docs/LumiSlotsMatrix.xlsx
+++ b/docs/LumiSlotsMatrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://totalparking.sharepoint.com/sites/PrjLumi/Shared Documents/50 tech🛠️/53 tech_others🛠️/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{91CEC09A-7635-45C8-ABCB-A5281F2486E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15E403A4-D293-4B84-8B04-E27E952C0130}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{91CEC09A-7635-45C8-ABCB-A5281F2486E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF7EB760-F4E3-4D91-B456-3FAE6CD6EC89}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{71B2C124-AEB6-4AF8-BB77-D639608321E5}"/>
   </bookViews>
@@ -782,7 +782,7 @@
         <v>65</v>
       </c>
       <c r="B14" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>30</v>
@@ -804,7 +804,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>34</v>
@@ -894,6 +894,33 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bb85ac0c-225e-4f04-a4a8-c731f560fa4f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <PIC xmlns="bb85ac0c-225e-4f04-a4a8-c731f560fa4f">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </PIC>
+    <TaxCatchAll xmlns="deb37b46-6cfb-45c9-b8e3-059b6c03190b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006D5F4C936AABD44EAE6B54EF5B992FFF" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8d40a7f82d0b3a34fcc2b1b40ac02e85">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bb85ac0c-225e-4f04-a4a8-c731f560fa4f" xmlns:ns3="deb37b46-6cfb-45c9-b8e3-059b6c03190b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9059d7e4bf0acffd8a347fb052b84781" ns2:_="" ns3:_="">
     <xsd:import namespace="bb85ac0c-225e-4f04-a4a8-c731f560fa4f"/>
@@ -1108,41 +1135,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bb85ac0c-225e-4f04-a4a8-c731f560fa4f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <PIC xmlns="bb85ac0c-225e-4f04-a4a8-c731f560fa4f">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </PIC>
-    <TaxCatchAll xmlns="deb37b46-6cfb-45c9-b8e3-059b6c03190b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AA34867-36D0-4047-94BB-FC4CD05290C2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50B93BE7-C660-495A-89A3-776E5FDB572E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="bb85ac0c-225e-4f04-a4a8-c731f560fa4f"/>
+    <ds:schemaRef ds:uri="deb37b46-6cfb-45c9-b8e3-059b6c03190b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E44F80C3-FB35-40AB-B558-1BFB944A8507}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E44F80C3-FB35-40AB-B558-1BFB944A8507}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50B93BE7-C660-495A-89A3-776E5FDB572E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AA34867-36D0-4047-94BB-FC4CD05290C2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="bb85ac0c-225e-4f04-a4a8-c731f560fa4f"/>
+    <ds:schemaRef ds:uri="deb37b46-6cfb-45c9-b8e3-059b6c03190b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/docs/LumiSlotsMatrix.xlsx
+++ b/docs/LumiSlotsMatrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://totalparking.sharepoint.com/sites/PrjLumi/Shared Documents/50 tech🛠️/53 tech_others🛠️/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{91CEC09A-7635-45C8-ABCB-A5281F2486E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF7EB760-F4E3-4D91-B456-3FAE6CD6EC89}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{91CEC09A-7635-45C8-ABCB-A5281F2486E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BC74E90-BF2A-436A-81F1-CF76A52CD65F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{71B2C124-AEB6-4AF8-BB77-D639608321E5}"/>
+    <workbookView xWindow="2580" yWindow="2580" windowWidth="17280" windowHeight="8880" xr2:uid="{71B2C124-AEB6-4AF8-BB77-D639608321E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="56">
   <si>
     <t>led</t>
   </si>
@@ -81,15 +81,6 @@
     <t>Z2.2.1~7</t>
   </si>
   <si>
-    <t>31~54</t>
-  </si>
-  <si>
-    <t>1~10,16~20</t>
-  </si>
-  <si>
-    <t>Z1.1.1~4,  Z1.2.1~4</t>
-  </si>
-  <si>
     <t>38~49</t>
   </si>
   <si>
@@ -199,6 +190,9 @@
   </si>
   <si>
     <t>Id cảm biến từ c đến f</t>
+  </si>
+  <si>
+    <t>33~54</t>
   </si>
 </sst>
 </file>
@@ -562,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0612BED7-8A1F-4745-AE80-ED3C8E0544AB}">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="35.44140625" style="1" customWidth="1"/>
@@ -585,10 +579,10 @@
         <v>6</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -608,7 +602,7 @@
         <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -628,7 +622,7 @@
         <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -645,7 +639,7 @@
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -662,10 +656,10 @@
         <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -676,10 +670,10 @@
         <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -693,10 +687,10 @@
         <v>17</v>
       </c>
       <c r="E7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -707,185 +701,174 @@
         <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>56</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" t="s">
         <v>19</v>
-      </c>
-      <c r="D9" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>54</v>
+      </c>
+      <c r="B12" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>51</v>
-      </c>
-      <c r="B11" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
         <v>5</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>65</v>
-      </c>
-      <c r="B14" t="s">
-        <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>67</v>
+      </c>
+      <c r="B16" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s">
         <v>33</v>
-      </c>
-      <c r="D15" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" t="s">
         <v>35</v>
-      </c>
-      <c r="D17" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>57</v>
-      </c>
-      <c r="B18" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>66</v>
+      </c>
       <c r="B20" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D20" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>66</v>
-      </c>
-      <c r="B21" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="D21" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -894,33 +877,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bb85ac0c-225e-4f04-a4a8-c731f560fa4f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <PIC xmlns="bb85ac0c-225e-4f04-a4a8-c731f560fa4f">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </PIC>
-    <TaxCatchAll xmlns="deb37b46-6cfb-45c9-b8e3-059b6c03190b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006D5F4C936AABD44EAE6B54EF5B992FFF" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8d40a7f82d0b3a34fcc2b1b40ac02e85">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bb85ac0c-225e-4f04-a4a8-c731f560fa4f" xmlns:ns3="deb37b46-6cfb-45c9-b8e3-059b6c03190b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9059d7e4bf0acffd8a347fb052b84781" ns2:_="" ns3:_="">
     <xsd:import namespace="bb85ac0c-225e-4f04-a4a8-c731f560fa4f"/>
@@ -1135,26 +1091,34 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50B93BE7-C660-495A-89A3-776E5FDB572E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="bb85ac0c-225e-4f04-a4a8-c731f560fa4f"/>
-    <ds:schemaRef ds:uri="deb37b46-6cfb-45c9-b8e3-059b6c03190b"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E44F80C3-FB35-40AB-B558-1BFB944A8507}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bb85ac0c-225e-4f04-a4a8-c731f560fa4f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <PIC xmlns="bb85ac0c-225e-4f04-a4a8-c731f560fa4f">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </PIC>
+    <TaxCatchAll xmlns="deb37b46-6cfb-45c9-b8e3-059b6c03190b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AA34867-36D0-4047-94BB-FC4CD05290C2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1171,4 +1135,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E44F80C3-FB35-40AB-B558-1BFB944A8507}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50B93BE7-C660-495A-89A3-776E5FDB572E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="bb85ac0c-225e-4f04-a4a8-c731f560fa4f"/>
+    <ds:schemaRef ds:uri="deb37b46-6cfb-45c9-b8e3-059b6c03190b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>